--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Dosage</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Dosage|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -417,7 +417,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -438,7 +438,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -518,7 +518,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -545,7 +545,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -610,7 +610,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -774,7 +774,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -847,7 +847,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -856,7 +856,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -879,7 +879,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -907,7 +907,7 @@
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -929,7 +929,7 @@
     <t>Dosage.maxDosePerAdministration</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1268,7 +1268,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.55078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.54296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1283,7 +1283,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Dosage|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Dosage</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -417,7 +417,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -438,7 +438,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -518,7 +518,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -545,7 +545,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -610,7 +610,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -774,7 +774,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -847,7 +847,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -856,7 +856,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -879,7 +879,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity|4.0.1}</t>
+RangeQuantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -907,7 +907,7 @@
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -929,7 +929,7 @@
     <t>Dosage.maxDosePerAdministration</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1268,7 +1268,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="76.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.55078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1283,7 +1283,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
